--- a/excels/2급_분개문제(AI).xlsx
+++ b/excels/2급_분개문제(AI).xlsx
@@ -1,21 +1,20 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-20T11:45:45Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-20T11:45:45Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
@@ -125,7 +124,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -408,7 +407,23 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="문제" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="정답및해설" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12444,7 +12459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13050,7 +13065,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -13363,7 +13378,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13602,7 +13617,7 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -13637,7 +13652,7 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -13775,7 +13790,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -14358,7 +14373,7 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -14393,7 +14408,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14595,7 +14610,7 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -15870,7 +15885,7 @@
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -16241,7 +16256,7 @@
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -16616,7 +16631,7 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -16859,7 +16874,7 @@
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -16995,7 +17010,7 @@
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -17368,7 +17383,7 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -17403,7 +17418,7 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -17776,7 +17791,7 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -17811,7 +17826,7 @@
       <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -17912,7 +17927,7 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -17978,7 +17993,7 @@
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -18013,7 +18028,7 @@
       <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -18046,7 +18061,7 @@
       <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -18417,7 +18432,7 @@
       <c r="C175" t="inlineStr"/>
       <c r="D175" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -18891,7 +18906,7 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -19229,7 +19244,7 @@
       <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -19499,7 +19514,7 @@
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -20795,7 +20810,7 @@
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20964,7 +20979,7 @@
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -21512,7 +21527,7 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -21615,7 +21630,7 @@
       <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -21784,7 +21799,7 @@
       <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -21918,7 +21933,7 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -21951,7 +21966,7 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -22365,7 +22380,7 @@
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -22435,7 +22450,7 @@
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -22505,7 +22520,7 @@
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -22538,7 +22553,7 @@
       <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -22606,7 +22621,7 @@
       <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -23053,7 +23068,7 @@
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -23465,7 +23480,7 @@
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -23498,7 +23513,7 @@
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -23700,7 +23715,7 @@
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -23803,7 +23818,7 @@
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -24524,7 +24539,7 @@
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -24629,7 +24644,7 @@
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -25385,7 +25400,7 @@
       <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -25451,7 +25466,7 @@
       <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -25484,7 +25499,7 @@
       <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -25898,7 +25913,7 @@
       <c r="C394" t="inlineStr"/>
       <c r="D394" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -26034,7 +26049,7 @@
       <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -26236,7 +26251,7 @@
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -26479,7 +26494,7 @@
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -26986,7 +27001,7 @@
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -27571,7 +27586,7 @@
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -27641,7 +27656,7 @@
       <c r="C445" t="inlineStr"/>
       <c r="D445" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -27810,7 +27825,7 @@
       <c r="C450" t="inlineStr"/>
       <c r="D450" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
@@ -28018,7 +28033,7 @@
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
@@ -28193,7 +28208,7 @@
       <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
@@ -28467,7 +28482,7 @@
       <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -28809,7 +28824,7 @@
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -28914,7 +28929,7 @@
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -29122,7 +29137,7 @@
       <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
@@ -29155,7 +29170,7 @@
       <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -29530,7 +29545,7 @@
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -29705,7 +29720,7 @@
       <c r="C505" t="inlineStr"/>
       <c r="D505" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
@@ -29979,7 +29994,7 @@
       <c r="C513" t="inlineStr"/>
       <c r="D513" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -30082,7 +30097,7 @@
       <c r="C516" t="inlineStr"/>
       <c r="D516" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -30117,7 +30132,7 @@
       <c r="C517" t="inlineStr"/>
       <c r="D517" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -30694,7 +30709,7 @@
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -30935,7 +30950,7 @@
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -31176,7 +31191,7 @@
       <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -31211,7 +31226,7 @@
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -31312,7 +31327,7 @@
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -31555,7 +31570,7 @@
       <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
@@ -31693,7 +31708,7 @@
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -32070,7 +32085,7 @@
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -32138,7 +32153,7 @@
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -32515,7 +32530,7 @@
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -32721,7 +32736,7 @@
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>급여</t>
+          <t>급여(판)</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -32995,7 +33010,7 @@
       <c r="C601" t="inlineStr"/>
       <c r="D601" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>통신비(판)</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
